--- a/data/nomad_bean_visualization.xlsx
+++ b/data/nomad_bean_visualization.xlsx
@@ -626,12 +626,12 @@
       </c>
       <c r="E4" s="4" t="inlineStr">
         <is>
-          <t>04-08-2025</t>
+          <t>8/4/2025</t>
         </is>
       </c>
       <c r="F4" s="4" t="inlineStr">
         <is>
-          <t>08.05.2025</t>
+          <t>May 8, 2025</t>
         </is>
       </c>
       <c r="G4" s="4" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>Priya Reyes</t>
+          <t xml:space="preserve">Priya Reyes </t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>26.04.2025</t>
+          <t>26-Apr-2025</t>
         </is>
       </c>
       <c r="G5" s="3" t="inlineStr">
@@ -785,12 +785,12 @@
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>2025-06-08</t>
+          <t>Jun 8, 2025</t>
         </is>
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>06-08-2025</t>
+          <t>8/6/2025</t>
         </is>
       </c>
       <c r="G7" s="3" t="inlineStr">
@@ -890,17 +890,17 @@
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>Explorer</t>
+          <t xml:space="preserve">Explorer </t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>04-20-2025</t>
+          <t>April 20, 2025</t>
         </is>
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>20.05.2025</t>
+          <t>20-May-2025</t>
         </is>
       </c>
       <c r="G9" s="3" t="inlineStr">
@@ -1005,12 +1005,12 @@
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>2025-03-27</t>
+          <t>Mar 27, 2025</t>
         </is>
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t>04-27-2025</t>
+          <t>27/4/2025</t>
         </is>
       </c>
       <c r="G11" s="3" t="inlineStr">
@@ -1172,7 +1172,7 @@
       </c>
       <c r="E14" s="4" t="inlineStr">
         <is>
-          <t>2025-04-07</t>
+          <t>April 7, 2025</t>
         </is>
       </c>
       <c r="F14" s="4" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="H14" s="4" t="inlineStr">
         <is>
-          <t>Paid</t>
+          <t xml:space="preserve">Paid </t>
         </is>
       </c>
       <c r="I14" s="4" t="inlineStr">
@@ -1230,7 +1230,7 @@
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
-          <t>2025-04-15</t>
+          <t>15-Apr-2025</t>
         </is>
       </c>
       <c r="G15" s="3" t="inlineStr">
@@ -1437,7 +1437,7 @@
       </c>
       <c r="E19" s="3" t="inlineStr">
         <is>
-          <t>2025-03-03</t>
+          <t>Mar 3, 2025</t>
         </is>
       </c>
       <c r="F19" s="3" t="inlineStr">
@@ -1490,12 +1490,12 @@
       </c>
       <c r="E20" s="4" t="inlineStr">
         <is>
-          <t>07.03.2025</t>
+          <t>7/3/2025</t>
         </is>
       </c>
       <c r="F20" s="4" t="inlineStr">
         <is>
-          <t>2025-04-07</t>
+          <t>April 7, 2025</t>
         </is>
       </c>
       <c r="G20" s="4" t="inlineStr">
@@ -1543,7 +1543,7 @@
       </c>
       <c r="E21" s="3" t="inlineStr">
         <is>
-          <t>2025-04-18</t>
+          <t>18-Apr-2025</t>
         </is>
       </c>
       <c r="F21" s="3" t="inlineStr">
@@ -1596,12 +1596,12 @@
       </c>
       <c r="E22" s="4" t="inlineStr">
         <is>
-          <t>05-28-2025</t>
+          <t>May 28, 2025</t>
         </is>
       </c>
       <c r="F22" s="4" t="inlineStr">
         <is>
-          <t>28.06.2025</t>
+          <t>28/6/2025</t>
         </is>
       </c>
       <c r="G22" s="4" t="inlineStr">
@@ -1649,7 +1649,7 @@
       </c>
       <c r="E23" s="3" t="inlineStr">
         <is>
-          <t>13.01.2025</t>
+          <t>January 13, 2025</t>
         </is>
       </c>
       <c r="F23" s="3" t="inlineStr">
@@ -1821,7 +1821,7 @@
       </c>
       <c r="F26" s="4" t="inlineStr">
         <is>
-          <t>2025-04-13</t>
+          <t>13-Apr-2025</t>
         </is>
       </c>
       <c r="G26" s="4" t="inlineStr">
@@ -1878,7 +1878,7 @@
       </c>
       <c r="F27" s="3" t="inlineStr">
         <is>
-          <t>2025-04-13</t>
+          <t>Apr 13, 2025</t>
         </is>
       </c>
       <c r="G27" s="3" t="inlineStr">
@@ -1930,12 +1930,12 @@
       </c>
       <c r="E28" s="4" t="inlineStr">
         <is>
-          <t>2025-02-17</t>
+          <t>17/2/2025</t>
         </is>
       </c>
       <c r="F28" s="4" t="inlineStr">
         <is>
-          <t>2025-03-17</t>
+          <t>March 17, 2025</t>
         </is>
       </c>
       <c r="G28" s="4" t="inlineStr">
@@ -2045,7 +2045,7 @@
       </c>
       <c r="F30" s="4" t="inlineStr">
         <is>
-          <t>06-17-2025</t>
+          <t>17-Jun-2025</t>
         </is>
       </c>
       <c r="G30" s="4" t="inlineStr">
@@ -2093,12 +2093,12 @@
       </c>
       <c r="E31" s="3" t="inlineStr">
         <is>
-          <t>06.04.2025</t>
+          <t>Apr 6, 2025</t>
         </is>
       </c>
       <c r="F31" s="3" t="inlineStr">
         <is>
-          <t>06.05.2025</t>
+          <t>6/5/2025</t>
         </is>
       </c>
       <c r="G31" s="3" t="inlineStr">
@@ -2151,7 +2151,7 @@
       </c>
       <c r="F32" s="4" t="inlineStr">
         <is>
-          <t>03-08-2025</t>
+          <t>March 8, 2025</t>
         </is>
       </c>
       <c r="G32" s="4" t="inlineStr">
@@ -2252,12 +2252,12 @@
       </c>
       <c r="E34" s="4" t="inlineStr">
         <is>
-          <t>02-20-2025</t>
+          <t>20-Feb-2025</t>
         </is>
       </c>
       <c r="F34" s="4" t="inlineStr">
         <is>
-          <t>03-20-2025</t>
+          <t>Mar 20, 2025</t>
         </is>
       </c>
       <c r="G34" s="4" t="inlineStr">
@@ -2314,7 +2314,7 @@
       </c>
       <c r="F35" s="3" t="inlineStr">
         <is>
-          <t>2025-04-25</t>
+          <t>25/4/2025</t>
         </is>
       </c>
       <c r="G35" s="3" t="inlineStr">
@@ -2358,12 +2358,12 @@
       </c>
       <c r="E36" s="4" t="inlineStr">
         <is>
-          <t>01-19-2025</t>
+          <t>January 19, 2025</t>
         </is>
       </c>
       <c r="F36" s="4" t="inlineStr">
         <is>
-          <t>19.02.2025</t>
+          <t>19-Feb-2025</t>
         </is>
       </c>
       <c r="G36" s="4" t="inlineStr">
@@ -2415,7 +2415,7 @@
       </c>
       <c r="E37" s="3" t="inlineStr">
         <is>
-          <t>23.05.2025</t>
+          <t>May 23, 2025</t>
         </is>
       </c>
       <c r="F37" s="3" t="inlineStr">
@@ -2468,7 +2468,7 @@
       </c>
       <c r="E38" s="4" t="inlineStr">
         <is>
-          <t>01-14-2025</t>
+          <t>14/1/2025</t>
         </is>
       </c>
       <c r="F38" s="4" t="inlineStr">
@@ -2525,12 +2525,12 @@
       </c>
       <c r="E39" s="3" t="inlineStr">
         <is>
-          <t>28.03.2025</t>
+          <t>March 28, 2025</t>
         </is>
       </c>
       <c r="F39" s="3" t="inlineStr">
         <is>
-          <t>2025-04-28</t>
+          <t>28-Apr-2025</t>
         </is>
       </c>
       <c r="G39" s="3" t="inlineStr">
@@ -2582,12 +2582,12 @@
       </c>
       <c r="E40" s="4" t="inlineStr">
         <is>
-          <t>2025-06-09</t>
+          <t>Jun 9, 2025</t>
         </is>
       </c>
       <c r="F40" s="4" t="inlineStr">
         <is>
-          <t>2025-06-09</t>
+          <t>9/6/2025</t>
         </is>
       </c>
       <c r="G40" s="4" t="inlineStr">
@@ -2644,7 +2644,7 @@
       </c>
       <c r="F41" s="3" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>June 17, 2025</t>
         </is>
       </c>
       <c r="G41" s="3" t="inlineStr">
@@ -2741,12 +2741,12 @@
       </c>
       <c r="E43" s="3" t="inlineStr">
         <is>
-          <t>10.05.2025</t>
+          <t>10-May-2025</t>
         </is>
       </c>
       <c r="F43" s="3" t="inlineStr">
         <is>
-          <t>2025-06-10</t>
+          <t>Jun 10, 2025</t>
         </is>
       </c>
       <c r="G43" s="3" t="inlineStr">
@@ -2851,12 +2851,12 @@
       </c>
       <c r="E45" s="3" t="inlineStr">
         <is>
-          <t>2025-04-10</t>
+          <t>10/4/2025</t>
         </is>
       </c>
       <c r="F45" s="3" t="inlineStr">
         <is>
-          <t>2025-05-10</t>
+          <t>May 10, 2025</t>
         </is>
       </c>
       <c r="G45" s="3" t="inlineStr">
@@ -2904,7 +2904,7 @@
       </c>
       <c r="E46" s="4" t="inlineStr">
         <is>
-          <t>10.04.2025</t>
+          <t>10-Apr-2025</t>
         </is>
       </c>
       <c r="F46" s="4" t="inlineStr">
@@ -3010,12 +3010,12 @@
       </c>
       <c r="E48" s="4" t="inlineStr">
         <is>
-          <t>2025-01-03</t>
+          <t>Jan 3, 2025</t>
         </is>
       </c>
       <c r="F48" s="4" t="inlineStr">
         <is>
-          <t>02-03-2025</t>
+          <t>3/2/2025</t>
         </is>
       </c>
       <c r="G48" s="4" t="inlineStr">
@@ -3230,7 +3230,7 @@
       </c>
       <c r="E52" s="4" t="inlineStr">
         <is>
-          <t>2025-02-16</t>
+          <t>February 16, 2025</t>
         </is>
       </c>
       <c r="F52" s="4" t="inlineStr">
@@ -3283,7 +3283,7 @@
       </c>
       <c r="E53" s="3" t="inlineStr">
         <is>
-          <t>04-11-2025</t>
+          <t>11-Apr-2025</t>
         </is>
       </c>
       <c r="F53" s="3" t="inlineStr">
@@ -3397,12 +3397,12 @@
       </c>
       <c r="E55" s="3" t="inlineStr">
         <is>
-          <t>04.04.2025</t>
+          <t>Apr 4, 2025</t>
         </is>
       </c>
       <c r="F55" s="3" t="inlineStr">
         <is>
-          <t>05-04-2025</t>
+          <t>4/5/2025</t>
         </is>
       </c>
       <c r="G55" s="3" t="inlineStr">
@@ -3450,7 +3450,7 @@
       </c>
       <c r="E56" s="4" t="inlineStr">
         <is>
-          <t>06-25-2025</t>
+          <t>June 25, 2025</t>
         </is>
       </c>
       <c r="F56" s="4" t="inlineStr">
@@ -3503,12 +3503,12 @@
       </c>
       <c r="E57" s="3" t="inlineStr">
         <is>
-          <t>2025-01-11</t>
+          <t>11-Jan-2025</t>
         </is>
       </c>
       <c r="F57" s="3" t="inlineStr">
         <is>
-          <t>02-11-2025</t>
+          <t>Feb 11, 2025</t>
         </is>
       </c>
       <c r="G57" s="3" t="inlineStr">
@@ -3560,12 +3560,12 @@
       </c>
       <c r="E58" s="4" t="inlineStr">
         <is>
-          <t>21.04.2025</t>
+          <t>21/4/2025</t>
         </is>
       </c>
       <c r="F58" s="4" t="inlineStr">
         <is>
-          <t>21.05.2025</t>
+          <t>May 21, 2025</t>
         </is>
       </c>
       <c r="G58" s="4" t="inlineStr">
@@ -3671,7 +3671,7 @@
       </c>
       <c r="F60" s="4" t="inlineStr">
         <is>
-          <t>20.03.2025</t>
+          <t>20-Mar-2025</t>
         </is>
       </c>
       <c r="G60" s="4" t="inlineStr">
@@ -3723,12 +3723,12 @@
       </c>
       <c r="E61" s="3" t="inlineStr">
         <is>
-          <t>2025-02-05</t>
+          <t>Feb 5, 2025</t>
         </is>
       </c>
       <c r="F61" s="3" t="inlineStr">
         <is>
-          <t>03-05-2025</t>
+          <t>5/3/2025</t>
         </is>
       </c>
       <c r="G61" s="3" t="inlineStr">
@@ -3834,7 +3834,7 @@
       </c>
       <c r="F63" s="3" t="inlineStr">
         <is>
-          <t>11.06.2025</t>
+          <t>June 11, 2025</t>
         </is>
       </c>
       <c r="G63" s="3" t="inlineStr">
@@ -3882,7 +3882,7 @@
       </c>
       <c r="E64" s="4" t="inlineStr">
         <is>
-          <t>15.04.2025</t>
+          <t>15-Apr-2025</t>
         </is>
       </c>
       <c r="F64" s="4" t="inlineStr"/>
@@ -3931,7 +3931,7 @@
       </c>
       <c r="E65" s="3" t="inlineStr">
         <is>
-          <t>2025-03-04</t>
+          <t>Mar 4, 2025</t>
         </is>
       </c>
       <c r="F65" s="3" t="inlineStr"/>
@@ -3985,7 +3985,7 @@
       </c>
       <c r="F66" s="4" t="inlineStr">
         <is>
-          <t>2025-03-26</t>
+          <t>26/3/2025</t>
         </is>
       </c>
       <c r="G66" s="4" t="inlineStr">
@@ -4094,12 +4094,12 @@
       </c>
       <c r="E68" s="4" t="inlineStr">
         <is>
-          <t>05-04-2025</t>
+          <t>May 4, 2025</t>
         </is>
       </c>
       <c r="F68" s="4" t="inlineStr">
         <is>
-          <t>06-04-2025</t>
+          <t>4-Jun-2025</t>
         </is>
       </c>
       <c r="G68" s="4" t="inlineStr">
@@ -4253,7 +4253,7 @@
       </c>
       <c r="E71" s="3" t="inlineStr">
         <is>
-          <t>26.03.2025</t>
+          <t>Mar 26, 2025</t>
         </is>
       </c>
       <c r="F71" s="3" t="inlineStr"/>

--- a/data/nomad_bean_visualization.xlsx
+++ b/data/nomad_bean_visualization.xlsx
@@ -573,12 +573,12 @@
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>4 Jun 2025</t>
+          <t>4/6/2025</t>
         </is>
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
-          <t>4 Jun 2025</t>
+          <t>4-Jun-2025</t>
         </is>
       </c>
       <c r="G3" s="3" t="inlineStr">
@@ -626,12 +626,12 @@
       </c>
       <c r="E4" s="4" t="inlineStr">
         <is>
-          <t>8/4/2025</t>
+          <t>8 Apr 2025</t>
         </is>
       </c>
       <c r="F4" s="4" t="inlineStr">
         <is>
-          <t>May 8, 2025</t>
+          <t>8.5.2025</t>
         </is>
       </c>
       <c r="G4" s="4" t="inlineStr">
@@ -679,12 +679,12 @@
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>March 26, 2025</t>
+          <t>26-3-2025</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>26-Apr-2025</t>
+          <t>26 Apr, 2025</t>
         </is>
       </c>
       <c r="G5" s="3" t="inlineStr">
@@ -732,12 +732,12 @@
       </c>
       <c r="E6" s="4" t="inlineStr">
         <is>
-          <t>March 3, 2025</t>
+          <t>3/3/2025</t>
         </is>
       </c>
       <c r="F6" s="4" t="inlineStr">
         <is>
-          <t>April 3, 2025</t>
+          <t>3-Apr-2025</t>
         </is>
       </c>
       <c r="G6" s="4" t="inlineStr">
@@ -785,12 +785,12 @@
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>Jun 8, 2025</t>
+          <t>8 Jun 2025</t>
         </is>
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>8/6/2025</t>
+          <t>8.6.2025</t>
         </is>
       </c>
       <c r="G7" s="3" t="inlineStr">
@@ -842,12 +842,12 @@
       </c>
       <c r="E8" s="4" t="inlineStr">
         <is>
-          <t>15/06/2025</t>
+          <t>15-6-2025</t>
         </is>
       </c>
       <c r="F8" s="4" t="inlineStr">
         <is>
-          <t>15/06/2025</t>
+          <t>15 Jun, 2025</t>
         </is>
       </c>
       <c r="G8" s="4" t="inlineStr">
@@ -895,7 +895,7 @@
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>April 20, 2025</t>
+          <t>20/4/2025</t>
         </is>
       </c>
       <c r="F9" s="3" t="inlineStr">
@@ -953,7 +953,7 @@
       </c>
       <c r="F10" s="4" t="inlineStr">
         <is>
-          <t>9 Jun 2025</t>
+          <t>9.6.2025</t>
         </is>
       </c>
       <c r="G10" s="4" t="inlineStr">
@@ -1005,12 +1005,12 @@
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>Mar 27, 2025</t>
+          <t>27-3-2025</t>
         </is>
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t>27/4/2025</t>
+          <t>27 Apr, 2025</t>
         </is>
       </c>
       <c r="G11" s="3" t="inlineStr">
@@ -1062,12 +1062,12 @@
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>18 Feb 2025</t>
+          <t>18/2/2025</t>
         </is>
       </c>
       <c r="F12" s="4" t="inlineStr">
         <is>
-          <t>18/03/2025</t>
+          <t>18-Mar-2025</t>
         </is>
       </c>
       <c r="G12" s="4" t="inlineStr">
@@ -1120,7 +1120,7 @@
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
-          <t>February 23, 2025</t>
+          <t>23.2.2025</t>
         </is>
       </c>
       <c r="G13" s="3" t="inlineStr">
@@ -1172,12 +1172,12 @@
       </c>
       <c r="E14" s="4" t="inlineStr">
         <is>
-          <t>April 7, 2025</t>
+          <t>7-4-2025</t>
         </is>
       </c>
       <c r="F14" s="4" t="inlineStr">
         <is>
-          <t>07/05/2025</t>
+          <t>7 May, 2025</t>
         </is>
       </c>
       <c r="G14" s="4" t="inlineStr">
@@ -1225,7 +1225,7 @@
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
-          <t>15/03/2025</t>
+          <t>15/3/2025</t>
         </is>
       </c>
       <c r="F15" s="3" t="inlineStr">
@@ -1278,12 +1278,12 @@
       </c>
       <c r="E16" s="4" t="inlineStr">
         <is>
-          <t>26/03/2025</t>
+          <t>26 Mar 2025</t>
         </is>
       </c>
       <c r="F16" s="4" t="inlineStr">
         <is>
-          <t>26/04/2025</t>
+          <t>26.4.2025</t>
         </is>
       </c>
       <c r="G16" s="4" t="inlineStr">
@@ -1331,7 +1331,7 @@
       </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
-          <t>06/05/2025</t>
+          <t>6-5-2025</t>
         </is>
       </c>
       <c r="F17" s="3" t="inlineStr"/>
@@ -1384,12 +1384,12 @@
       </c>
       <c r="E18" s="4" t="inlineStr">
         <is>
-          <t>09/03/2025</t>
+          <t>9 Mar, 2025</t>
         </is>
       </c>
       <c r="F18" s="4" t="inlineStr">
         <is>
-          <t>9 Apr 2025</t>
+          <t>9/4/2025</t>
         </is>
       </c>
       <c r="G18" s="4" t="inlineStr">
@@ -1437,12 +1437,12 @@
       </c>
       <c r="E19" s="3" t="inlineStr">
         <is>
-          <t>Mar 3, 2025</t>
+          <t>3-Mar-2025</t>
         </is>
       </c>
       <c r="F19" s="3" t="inlineStr">
         <is>
-          <t>03/04/2025</t>
+          <t>3 Apr 2025</t>
         </is>
       </c>
       <c r="G19" s="3" t="inlineStr">
@@ -1490,12 +1490,12 @@
       </c>
       <c r="E20" s="4" t="inlineStr">
         <is>
-          <t>7/3/2025</t>
+          <t>7.3.2025</t>
         </is>
       </c>
       <c r="F20" s="4" t="inlineStr">
         <is>
-          <t>April 7, 2025</t>
+          <t>7-4-2025</t>
         </is>
       </c>
       <c r="G20" s="4" t="inlineStr">
@@ -1543,12 +1543,12 @@
       </c>
       <c r="E21" s="3" t="inlineStr">
         <is>
-          <t>18-Apr-2025</t>
+          <t>18 Apr, 2025</t>
         </is>
       </c>
       <c r="F21" s="3" t="inlineStr">
         <is>
-          <t>18/05/2025</t>
+          <t>18/5/2025</t>
         </is>
       </c>
       <c r="G21" s="3" t="inlineStr">
@@ -1596,12 +1596,12 @@
       </c>
       <c r="E22" s="4" t="inlineStr">
         <is>
-          <t>May 28, 2025</t>
+          <t>28-May-2025</t>
         </is>
       </c>
       <c r="F22" s="4" t="inlineStr">
         <is>
-          <t>28/6/2025</t>
+          <t>28 Jun 2025</t>
         </is>
       </c>
       <c r="G22" s="4" t="inlineStr">
@@ -1649,12 +1649,12 @@
       </c>
       <c r="E23" s="3" t="inlineStr">
         <is>
-          <t>January 13, 2025</t>
+          <t>13.1.2025</t>
         </is>
       </c>
       <c r="F23" s="3" t="inlineStr">
         <is>
-          <t>13/02/2025</t>
+          <t>13-2-2025</t>
         </is>
       </c>
       <c r="G23" s="3" t="inlineStr">
@@ -1706,12 +1706,12 @@
       </c>
       <c r="E24" s="4" t="inlineStr">
         <is>
-          <t>11 May 2025</t>
+          <t>11 May, 2025</t>
         </is>
       </c>
       <c r="F24" s="4" t="inlineStr">
         <is>
-          <t>11/06/2025</t>
+          <t>11/6/2025</t>
         </is>
       </c>
       <c r="G24" s="4" t="inlineStr">
@@ -1759,12 +1759,12 @@
       </c>
       <c r="E25" s="3" t="inlineStr">
         <is>
-          <t>January 17, 2025</t>
+          <t>17-Jan-2025</t>
         </is>
       </c>
       <c r="F25" s="3" t="inlineStr">
         <is>
-          <t>February 17, 2025</t>
+          <t>17 Feb 2025</t>
         </is>
       </c>
       <c r="G25" s="3" t="inlineStr">
@@ -1816,12 +1816,12 @@
       </c>
       <c r="E26" s="4" t="inlineStr">
         <is>
-          <t>13 Mar 2025</t>
+          <t>13.3.2025</t>
         </is>
       </c>
       <c r="F26" s="4" t="inlineStr">
         <is>
-          <t>13-Apr-2025</t>
+          <t>13-4-2025</t>
         </is>
       </c>
       <c r="G26" s="4" t="inlineStr">
@@ -1873,12 +1873,12 @@
       </c>
       <c r="E27" s="3" t="inlineStr">
         <is>
-          <t>13 Mar 2025</t>
+          <t>13 Mar, 2025</t>
         </is>
       </c>
       <c r="F27" s="3" t="inlineStr">
         <is>
-          <t>Apr 13, 2025</t>
+          <t>13/4/2025</t>
         </is>
       </c>
       <c r="G27" s="3" t="inlineStr">
@@ -1930,12 +1930,12 @@
       </c>
       <c r="E28" s="4" t="inlineStr">
         <is>
-          <t>17/2/2025</t>
+          <t>17-Feb-2025</t>
         </is>
       </c>
       <c r="F28" s="4" t="inlineStr">
         <is>
-          <t>March 17, 2025</t>
+          <t>17 Mar 2025</t>
         </is>
       </c>
       <c r="G28" s="4" t="inlineStr">
@@ -1983,12 +1983,12 @@
       </c>
       <c r="E29" s="3" t="inlineStr">
         <is>
-          <t>20/04/2025</t>
+          <t>20.4.2025</t>
         </is>
       </c>
       <c r="F29" s="3" t="inlineStr">
         <is>
-          <t>20/05/2025</t>
+          <t>20-5-2025</t>
         </is>
       </c>
       <c r="G29" s="3" t="inlineStr">
@@ -2040,12 +2040,12 @@
       </c>
       <c r="E30" s="4" t="inlineStr">
         <is>
-          <t>June 17, 2025</t>
+          <t>17 Jun, 2025</t>
         </is>
       </c>
       <c r="F30" s="4" t="inlineStr">
         <is>
-          <t>17-Jun-2025</t>
+          <t>17/6/2025</t>
         </is>
       </c>
       <c r="G30" s="4" t="inlineStr">
@@ -2093,12 +2093,12 @@
       </c>
       <c r="E31" s="3" t="inlineStr">
         <is>
-          <t>Apr 6, 2025</t>
+          <t>6-Apr-2025</t>
         </is>
       </c>
       <c r="F31" s="3" t="inlineStr">
         <is>
-          <t>6/5/2025</t>
+          <t>6 May 2025</t>
         </is>
       </c>
       <c r="G31" s="3" t="inlineStr">
@@ -2146,12 +2146,12 @@
       </c>
       <c r="E32" s="4" t="inlineStr">
         <is>
-          <t>8 Feb 2025</t>
+          <t>8.2.2025</t>
         </is>
       </c>
       <c r="F32" s="4" t="inlineStr">
         <is>
-          <t>March 8, 2025</t>
+          <t>8-3-2025</t>
         </is>
       </c>
       <c r="G32" s="4" t="inlineStr">
@@ -2199,12 +2199,12 @@
       </c>
       <c r="E33" s="3" t="inlineStr">
         <is>
-          <t>April 16, 2025</t>
+          <t>16 Apr, 2025</t>
         </is>
       </c>
       <c r="F33" s="3" t="inlineStr">
         <is>
-          <t>16/05/2025</t>
+          <t>16/5/2025</t>
         </is>
       </c>
       <c r="G33" s="3" t="inlineStr">
@@ -2257,7 +2257,7 @@
       </c>
       <c r="F34" s="4" t="inlineStr">
         <is>
-          <t>Mar 20, 2025</t>
+          <t>20 Mar 2025</t>
         </is>
       </c>
       <c r="G34" s="4" t="inlineStr">
@@ -2309,12 +2309,12 @@
       </c>
       <c r="E35" s="3" t="inlineStr">
         <is>
-          <t>25/03/2025</t>
+          <t>25.3.2025</t>
         </is>
       </c>
       <c r="F35" s="3" t="inlineStr">
         <is>
-          <t>25/4/2025</t>
+          <t>25-4-2025</t>
         </is>
       </c>
       <c r="G35" s="3" t="inlineStr">
@@ -2358,12 +2358,12 @@
       </c>
       <c r="E36" s="4" t="inlineStr">
         <is>
-          <t>January 19, 2025</t>
+          <t>19 Jan, 2025</t>
         </is>
       </c>
       <c r="F36" s="4" t="inlineStr">
         <is>
-          <t>19-Feb-2025</t>
+          <t>19/2/2025</t>
         </is>
       </c>
       <c r="G36" s="4" t="inlineStr">
@@ -2415,12 +2415,12 @@
       </c>
       <c r="E37" s="3" t="inlineStr">
         <is>
-          <t>May 23, 2025</t>
+          <t>23-May-2025</t>
         </is>
       </c>
       <c r="F37" s="3" t="inlineStr">
         <is>
-          <t>23/06/2025</t>
+          <t>23 Jun 2025</t>
         </is>
       </c>
       <c r="G37" s="3" t="inlineStr">
@@ -2468,12 +2468,12 @@
       </c>
       <c r="E38" s="4" t="inlineStr">
         <is>
-          <t>14/1/2025</t>
+          <t>14.1.2025</t>
         </is>
       </c>
       <c r="F38" s="4" t="inlineStr">
         <is>
-          <t>14 Feb 2025</t>
+          <t>14-2-2025</t>
         </is>
       </c>
       <c r="G38" s="4" t="inlineStr">
@@ -2525,12 +2525,12 @@
       </c>
       <c r="E39" s="3" t="inlineStr">
         <is>
-          <t>March 28, 2025</t>
+          <t>28 Mar, 2025</t>
         </is>
       </c>
       <c r="F39" s="3" t="inlineStr">
         <is>
-          <t>28-Apr-2025</t>
+          <t>28/4/2025</t>
         </is>
       </c>
       <c r="G39" s="3" t="inlineStr">
@@ -2582,12 +2582,12 @@
       </c>
       <c r="E40" s="4" t="inlineStr">
         <is>
-          <t>Jun 9, 2025</t>
+          <t>9-Jun-2025</t>
         </is>
       </c>
       <c r="F40" s="4" t="inlineStr">
         <is>
-          <t>9/6/2025</t>
+          <t>9 Jun 2025</t>
         </is>
       </c>
       <c r="G40" s="4" t="inlineStr">
@@ -2639,12 +2639,12 @@
       </c>
       <c r="E41" s="3" t="inlineStr">
         <is>
-          <t>May 17, 2025</t>
+          <t>17.5.2025</t>
         </is>
       </c>
       <c r="F41" s="3" t="inlineStr">
         <is>
-          <t>June 17, 2025</t>
+          <t>17-6-2025</t>
         </is>
       </c>
       <c r="G41" s="3" t="inlineStr">
@@ -2692,7 +2692,7 @@
       </c>
       <c r="E42" s="4" t="inlineStr">
         <is>
-          <t>7 Feb 2025</t>
+          <t>7 Feb, 2025</t>
         </is>
       </c>
       <c r="F42" s="4" t="inlineStr"/>
@@ -2741,12 +2741,12 @@
       </c>
       <c r="E43" s="3" t="inlineStr">
         <is>
-          <t>10-May-2025</t>
+          <t>10/5/2025</t>
         </is>
       </c>
       <c r="F43" s="3" t="inlineStr">
         <is>
-          <t>Jun 10, 2025</t>
+          <t>10-Jun-2025</t>
         </is>
       </c>
       <c r="G43" s="3" t="inlineStr">
@@ -2803,7 +2803,7 @@
       </c>
       <c r="F44" s="4" t="inlineStr">
         <is>
-          <t>3 May 2025</t>
+          <t>3.5.2025</t>
         </is>
       </c>
       <c r="G44" s="4" t="inlineStr">
@@ -2851,12 +2851,12 @@
       </c>
       <c r="E45" s="3" t="inlineStr">
         <is>
-          <t>10/4/2025</t>
+          <t>10-4-2025</t>
         </is>
       </c>
       <c r="F45" s="3" t="inlineStr">
         <is>
-          <t>May 10, 2025</t>
+          <t>10 May, 2025</t>
         </is>
       </c>
       <c r="G45" s="3" t="inlineStr">
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E46" s="4" t="inlineStr">
         <is>
-          <t>10-Apr-2025</t>
+          <t>10/4/2025</t>
         </is>
       </c>
       <c r="F46" s="4" t="inlineStr">
         <is>
-          <t>May 10, 2025</t>
+          <t>10-May-2025</t>
         </is>
       </c>
       <c r="G46" s="4" t="inlineStr">
@@ -2957,7 +2957,7 @@
       </c>
       <c r="E47" s="3" t="inlineStr">
         <is>
-          <t>20/03/2025</t>
+          <t>20 Mar 2025</t>
         </is>
       </c>
       <c r="F47" s="3" t="inlineStr"/>
@@ -3010,12 +3010,12 @@
       </c>
       <c r="E48" s="4" t="inlineStr">
         <is>
-          <t>Jan 3, 2025</t>
+          <t>3.1.2025</t>
         </is>
       </c>
       <c r="F48" s="4" t="inlineStr">
         <is>
-          <t>3/2/2025</t>
+          <t>3-2-2025</t>
         </is>
       </c>
       <c r="G48" s="4" t="inlineStr">
@@ -3067,7 +3067,7 @@
       </c>
       <c r="E49" s="3" t="inlineStr">
         <is>
-          <t>16/01/2025</t>
+          <t>16 Jan, 2025</t>
         </is>
       </c>
       <c r="F49" s="3" t="inlineStr"/>
@@ -3120,12 +3120,12 @@
       </c>
       <c r="E50" s="4" t="inlineStr">
         <is>
-          <t>28/04/2025</t>
+          <t>28/4/2025</t>
         </is>
       </c>
       <c r="F50" s="4" t="inlineStr">
         <is>
-          <t>May 28, 2025</t>
+          <t>28-May-2025</t>
         </is>
       </c>
       <c r="G50" s="4" t="inlineStr">
@@ -3173,12 +3173,12 @@
       </c>
       <c r="E51" s="3" t="inlineStr">
         <is>
-          <t>15/03/2025</t>
+          <t>15 Mar 2025</t>
         </is>
       </c>
       <c r="F51" s="3" t="inlineStr">
         <is>
-          <t>15/04/2025</t>
+          <t>15.4.2025</t>
         </is>
       </c>
       <c r="G51" s="3" t="inlineStr">
@@ -3230,12 +3230,12 @@
       </c>
       <c r="E52" s="4" t="inlineStr">
         <is>
-          <t>February 16, 2025</t>
+          <t>16-2-2025</t>
         </is>
       </c>
       <c r="F52" s="4" t="inlineStr">
         <is>
-          <t>16 Mar 2025</t>
+          <t>16 Mar, 2025</t>
         </is>
       </c>
       <c r="G52" s="4" t="inlineStr">
@@ -3283,12 +3283,12 @@
       </c>
       <c r="E53" s="3" t="inlineStr">
         <is>
-          <t>11-Apr-2025</t>
+          <t>11/4/2025</t>
         </is>
       </c>
       <c r="F53" s="3" t="inlineStr">
         <is>
-          <t>11 May 2025</t>
+          <t>11-May-2025</t>
         </is>
       </c>
       <c r="G53" s="3" t="inlineStr">
@@ -3345,7 +3345,7 @@
       </c>
       <c r="F54" s="4" t="inlineStr">
         <is>
-          <t>08/06/2025</t>
+          <t>8.6.2025</t>
         </is>
       </c>
       <c r="G54" s="4" t="inlineStr">
@@ -3397,12 +3397,12 @@
       </c>
       <c r="E55" s="3" t="inlineStr">
         <is>
-          <t>Apr 4, 2025</t>
+          <t>4-4-2025</t>
         </is>
       </c>
       <c r="F55" s="3" t="inlineStr">
         <is>
-          <t>4/5/2025</t>
+          <t>4 May, 2025</t>
         </is>
       </c>
       <c r="G55" s="3" t="inlineStr">
@@ -3450,12 +3450,12 @@
       </c>
       <c r="E56" s="4" t="inlineStr">
         <is>
-          <t>June 25, 2025</t>
+          <t>25/6/2025</t>
         </is>
       </c>
       <c r="F56" s="4" t="inlineStr">
         <is>
-          <t>June 25, 2025</t>
+          <t>25-Jun-2025</t>
         </is>
       </c>
       <c r="G56" s="4" t="inlineStr">
@@ -3503,12 +3503,12 @@
       </c>
       <c r="E57" s="3" t="inlineStr">
         <is>
-          <t>11-Jan-2025</t>
+          <t>11 Jan 2025</t>
         </is>
       </c>
       <c r="F57" s="3" t="inlineStr">
         <is>
-          <t>Feb 11, 2025</t>
+          <t>11.2.2025</t>
         </is>
       </c>
       <c r="G57" s="3" t="inlineStr">
@@ -3560,12 +3560,12 @@
       </c>
       <c r="E58" s="4" t="inlineStr">
         <is>
-          <t>21/4/2025</t>
+          <t>21-4-2025</t>
         </is>
       </c>
       <c r="F58" s="4" t="inlineStr">
         <is>
-          <t>May 21, 2025</t>
+          <t>21 May, 2025</t>
         </is>
       </c>
       <c r="G58" s="4" t="inlineStr">
@@ -3613,12 +3613,12 @@
       </c>
       <c r="E59" s="3" t="inlineStr">
         <is>
-          <t>07/03/2025</t>
+          <t>7/3/2025</t>
         </is>
       </c>
       <c r="F59" s="3" t="inlineStr">
         <is>
-          <t>April 7, 2025</t>
+          <t>7-Apr-2025</t>
         </is>
       </c>
       <c r="G59" s="3" t="inlineStr">
@@ -3666,12 +3666,12 @@
       </c>
       <c r="E60" s="4" t="inlineStr">
         <is>
-          <t>20/02/2025</t>
+          <t>20 Feb 2025</t>
         </is>
       </c>
       <c r="F60" s="4" t="inlineStr">
         <is>
-          <t>20-Mar-2025</t>
+          <t>20.3.2025</t>
         </is>
       </c>
       <c r="G60" s="4" t="inlineStr">
@@ -3723,12 +3723,12 @@
       </c>
       <c r="E61" s="3" t="inlineStr">
         <is>
-          <t>Feb 5, 2025</t>
+          <t>5-2-2025</t>
         </is>
       </c>
       <c r="F61" s="3" t="inlineStr">
         <is>
-          <t>5/3/2025</t>
+          <t>5 Mar, 2025</t>
         </is>
       </c>
       <c r="G61" s="3" t="inlineStr">
@@ -3776,12 +3776,12 @@
       </c>
       <c r="E62" s="4" t="inlineStr">
         <is>
-          <t>28/04/2025</t>
+          <t>28/4/2025</t>
         </is>
       </c>
       <c r="F62" s="4" t="inlineStr">
         <is>
-          <t>May 28, 2025</t>
+          <t>28-May-2025</t>
         </is>
       </c>
       <c r="G62" s="4" t="inlineStr">
@@ -3829,12 +3829,12 @@
       </c>
       <c r="E63" s="3" t="inlineStr">
         <is>
-          <t>11/05/2025</t>
+          <t>11 May 2025</t>
         </is>
       </c>
       <c r="F63" s="3" t="inlineStr">
         <is>
-          <t>June 11, 2025</t>
+          <t>11.6.2025</t>
         </is>
       </c>
       <c r="G63" s="3" t="inlineStr">
@@ -3882,7 +3882,7 @@
       </c>
       <c r="E64" s="4" t="inlineStr">
         <is>
-          <t>15-Apr-2025</t>
+          <t>15-4-2025</t>
         </is>
       </c>
       <c r="F64" s="4" t="inlineStr"/>
@@ -3931,7 +3931,7 @@
       </c>
       <c r="E65" s="3" t="inlineStr">
         <is>
-          <t>Mar 4, 2025</t>
+          <t>4 Mar, 2025</t>
         </is>
       </c>
       <c r="F65" s="3" t="inlineStr"/>
@@ -3980,12 +3980,12 @@
       </c>
       <c r="E66" s="4" t="inlineStr">
         <is>
-          <t>26 Feb 2025</t>
+          <t>26/2/2025</t>
         </is>
       </c>
       <c r="F66" s="4" t="inlineStr">
         <is>
-          <t>26/3/2025</t>
+          <t>26-Mar-2025</t>
         </is>
       </c>
       <c r="G66" s="4" t="inlineStr">
@@ -4037,12 +4037,12 @@
       </c>
       <c r="E67" s="3" t="inlineStr">
         <is>
-          <t>05/01/2025</t>
+          <t>5 Jan 2025</t>
         </is>
       </c>
       <c r="F67" s="3" t="inlineStr">
         <is>
-          <t>5 Feb 2025</t>
+          <t>5.2.2025</t>
         </is>
       </c>
       <c r="G67" s="3" t="inlineStr">
@@ -4094,12 +4094,12 @@
       </c>
       <c r="E68" s="4" t="inlineStr">
         <is>
-          <t>May 4, 2025</t>
+          <t>4-5-2025</t>
         </is>
       </c>
       <c r="F68" s="4" t="inlineStr">
         <is>
-          <t>4-Jun-2025</t>
+          <t>4 Jun, 2025</t>
         </is>
       </c>
       <c r="G68" s="4" t="inlineStr">
@@ -4151,12 +4151,12 @@
       </c>
       <c r="E69" s="3" t="inlineStr">
         <is>
-          <t>May 5, 2025</t>
+          <t>5/5/2025</t>
         </is>
       </c>
       <c r="F69" s="3" t="inlineStr">
         <is>
-          <t>June 5, 2025</t>
+          <t>5-Jun-2025</t>
         </is>
       </c>
       <c r="G69" s="3" t="inlineStr">
@@ -4204,7 +4204,7 @@
       </c>
       <c r="E70" s="4" t="inlineStr">
         <is>
-          <t>08/04/2025</t>
+          <t>8 Apr 2025</t>
         </is>
       </c>
       <c r="F70" s="4" t="inlineStr"/>
@@ -4253,7 +4253,7 @@
       </c>
       <c r="E71" s="3" t="inlineStr">
         <is>
-          <t>Mar 26, 2025</t>
+          <t>26.3.2025</t>
         </is>
       </c>
       <c r="F71" s="3" t="inlineStr"/>
